--- a/Config/Luban/source/TbGlobal.xlsx
+++ b/Config/Luban/source/TbGlobal.xlsx
@@ -341,7 +341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O4"/>
+  <dimension ref="A1:P4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -359,6 +359,7 @@
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="33" customWidth="1" min="14" max="14"/>
     <col width="33" customWidth="1" min="15" max="15"/>
+    <col width="28" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -437,6 +438,11 @@
           <t>paintShapeNoiseScale</t>
         </is>
       </c>
+      <c r="P1" s="3" t="inlineStr">
+        <is>
+          <t>simulationRate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -514,6 +520,11 @@
           <t>float</t>
         </is>
       </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -589,6 +600,11 @@
       <c r="O3" s="6" t="inlineStr">
         <is>
           <t>墨水轮廓噪声频率，CPU 与 GPU 共用</t>
+        </is>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>玩法模拟和输入采样频率（Hz）</t>
         </is>
       </c>
     </row>
@@ -636,6 +652,9 @@
       <c r="O4" s="8" t="n">
         <v>110</v>
       </c>
+      <c r="P4" s="8" t="n">
+        <v>60</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Luban/source/TbGlobal.xlsx
+++ b/Config/Luban/source/TbGlobal.xlsx
@@ -341,7 +341,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:Q4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -360,6 +360,7 @@
     <col width="33" customWidth="1" min="14" max="14"/>
     <col width="33" customWidth="1" min="15" max="15"/>
     <col width="28" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -443,6 +444,11 @@
           <t>simulationRate</t>
         </is>
       </c>
+      <c r="Q1" s="3" t="inlineStr">
+        <is>
+          <t>aimCorrectionDistance</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -525,6 +531,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="Q2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1">
       <c r="A3" s="6" t="inlineStr">
@@ -605,6 +616,11 @@
       <c r="P3" s="6" t="inlineStr">
         <is>
           <t>玩法模拟和输入采样频率（Hz）</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>瞄准：修正点距逻辑摄像机的距离（米，必须大于0）</t>
         </is>
       </c>
     </row>
@@ -655,6 +671,9 @@
       <c r="P4" s="8" t="n">
         <v>60</v>
       </c>
+      <c r="Q4" s="8" t="n">
+        <v>6</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Luban/source/TbGlobal.xlsx
+++ b/Config/Luban/source/TbGlobal.xlsx
@@ -1488,7 +1488,7 @@
         <v>60</v>
       </c>
       <c r="Q4" s="5">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/source/TbGlobal.xlsx
+++ b/Config/Luban/source/TbGlobal.xlsx
@@ -1271,7 +1271,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q4"/>
+  <dimension ref="A1:R4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
     <col min="1" max="13" width="22" customWidth="1"/>
@@ -1331,6 +1331,11 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>aimFarCorrectionDistance</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14.5" spans="1:17">
       <c r="A2" s="1" t="s">
@@ -1384,6 +1389,11 @@
       <c r="Q2" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1" spans="1:17">
       <c r="A3" s="2" t="s">
@@ -1434,8 +1444,15 @@
       <c r="P3" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>36</v>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>瞄准：近端收敛点距逻辑摄像机的距离（米，必须大于0）</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>瞄准：无命中时远端收敛距离（米，不小于近端距离）</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="14.5" spans="1:17">
@@ -1489,6 +1506,9 @@
       </c>
       <c r="Q4" s="5">
         <v>6</v>
+      </c>
+      <c r="R4" s="5" t="n">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/Config/Luban/source/TbGlobal.xlsx
+++ b/Config/Luban/source/TbGlobal.xlsx
@@ -1,336 +1,195 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\XPHUNITY\ProjectSplatoon\Config\Luban\source\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="17680"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="17680" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Global" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>defaultModeId</t>
-  </si>
-  <si>
-    <t>networkTickRate</t>
-  </si>
-  <si>
-    <t>projectileStepRate</t>
-  </si>
-  <si>
-    <t>defaultPort</t>
-  </si>
-  <si>
-    <t>connectionTimeout</t>
-  </si>
-  <si>
-    <t>inputTimeout</t>
-  </si>
-  <si>
-    <t>snapshotChunkBytes</t>
-  </si>
-  <si>
-    <t>chunksPerFrame</t>
-  </si>
-  <si>
-    <t>checkpointStamps</t>
-  </si>
-  <si>
-    <t>paintThreshold</t>
-  </si>
-  <si>
-    <t>maxPaintMemoryMiB</t>
-  </si>
-  <si>
-    <t>paintWorldUvScale</t>
-  </si>
-  <si>
-    <t>paintShapeNoiseScale</t>
-  </si>
-  <si>
-    <t>simulationRate</t>
-  </si>
-  <si>
-    <t>aimCorrectionDistance</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>唯一全局记录 ID，固定 1</t>
-  </si>
-  <si>
-    <t>默认房间模式 ID</t>
-  </si>
-  <si>
-    <t>网络频率（Hz）</t>
-  </si>
-  <si>
-    <t>弹道子步频率（Hz）</t>
-  </si>
-  <si>
-    <t>默认 UDP 端口</t>
-  </si>
-  <si>
-    <t>连接超时（秒）</t>
-  </si>
-  <si>
-    <t>输入失联停止（秒）</t>
-  </si>
-  <si>
-    <t>每个快照分块的最大字节数</t>
-  </si>
-  <si>
-    <t>每帧最多发送的快照块数</t>
-  </si>
-  <si>
-    <t>触发滚动检查点的涂色事件数</t>
-  </si>
-  <si>
-    <t>地面归属阈值（0 到 1）</t>
-  </si>
-  <si>
-    <t>涂色 RT 内存预算（MiB）</t>
-  </si>
-  <si>
-    <t>墨水细节坐标密度（UV/米），影响覆盖边缘</t>
-  </si>
-  <si>
-    <t>墨水轮廓噪声频率，CPU 与 GPU 共用</t>
-  </si>
-  <si>
-    <t>玩法模拟和输入采样频率（Hz）</t>
-  </si>
-  <si>
-    <t>瞄准：修正点距逻辑摄像机的距离（米，必须大于0）</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="5">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="0.000000"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
   </numFmts>
   <fonts count="23">
     <font>
-      <sz val="11"/>
       <name val="Carlito"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
       <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+    </font>
+    <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="Calibri"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <charset val="0"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="35">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -642,164 +501,169 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="49" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="49" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="49" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="49"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1046,7 +910,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1055,7 +919,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1068,11 +932,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1269,250 +1196,388 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:R4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T4"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
-    <col min="1" max="13" width="22" customWidth="1"/>
-    <col min="14" max="15" width="33" customWidth="1"/>
-    <col min="16" max="16" width="40" customWidth="1"/>
+    <col width="22" customWidth="1" style="6" min="1" max="13"/>
+    <col width="33" customWidth="1" style="6" min="14" max="15"/>
+    <col width="40" customWidth="1" style="6" min="16" max="16"/>
+    <col width="64" customWidth="1" style="6" min="19" max="19"/>
+    <col width="64" customWidth="1" style="6" min="20" max="20"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.5" spans="1:17">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="14.5" customHeight="1" s="6">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>defaultModeId</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>networkTickRate</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>projectileStepRate</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>defaultPort</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>connectionTimeout</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>inputTimeout</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>snapshotChunkBytes</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>chunksPerFrame</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>checkpointStamps</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>paintThreshold</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>maxPaintMemoryMiB</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>paintWorldUvScale</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>paintShapeNoiseScale</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>simulationRate</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>aimCorrectionDistance</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>aimFarCorrectionDistance</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>snapshotBytesPerSecond</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>snapshotMaxInFlightRecords</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="14.5" customHeight="1" s="6">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="C2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="D2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="E2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="G2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="J2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="N2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="O2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="P2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="Q2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="R2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="T2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="42" customHeight="1" s="6">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>##</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>唯一全局记录 ID，固定 1</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>默认房间模式 ID</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>网络频率（Hz）</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>弹道子步频率（Hz）</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>默认 UDP 端口</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>连接超时（秒）</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>输入失联停止（秒）</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>每个快照分块的最大字节数</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>每帧最多发送的快照块数</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>触发滚动检查点的涂色事件数</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>地面归属阈值（0 到 1）</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>涂色 RT 内存预算（MiB）</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>墨水细节坐标密度（UV/米），影响覆盖边缘</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>墨水轮廓噪声频率，CPU 与 GPU 共用</t>
+        </is>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>玩法模拟和输入采样频率（Hz）</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>瞄准：近端收敛点距逻辑摄像机的距离（米，必须大于0）</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>瞄准：无命中时远端收敛距离（米，不小于近端距离）</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>全房间补同步载荷预算（字节/秒，必须大于0）</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>每客户端未确认补同步记录上限（条，1到32）</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="14.5" customHeight="1" s="6">
+      <c r="A4" s="3" t="inlineStr"/>
+      <c r="B4" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="C4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>30</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>7777</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>4096</v>
+      </c>
+      <c r="J4" s="3" t="n">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>aimFarCorrectionDistance</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="14.5" spans="1:17">
-      <c r="A2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="42" customHeight="1" spans="1:17">
-      <c r="A3" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>瞄准：近端收敛点距逻辑摄像机的距离（米，必须大于0）</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr">
-        <is>
-          <t>瞄准：无命中时远端收敛距离（米，不小于近端距离）</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="14.5" spans="1:17">
-      <c r="A4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="3">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3">
-        <v>1</v>
-      </c>
-      <c r="D4" s="3">
-        <v>30</v>
-      </c>
-      <c r="E4" s="3">
-        <v>120</v>
-      </c>
-      <c r="F4" s="3">
-        <v>7777</v>
-      </c>
-      <c r="G4" s="3">
-        <v>20</v>
-      </c>
-      <c r="H4" s="3">
-        <v>0.3</v>
-      </c>
-      <c r="I4" s="3">
-        <v>4096</v>
-      </c>
-      <c r="J4" s="3">
-        <v>8</v>
-      </c>
-      <c r="K4" s="3">
+      <c r="K4" s="3" t="n">
         <v>512</v>
       </c>
-      <c r="L4" s="3">
+      <c r="L4" s="3" t="n">
         <v>0.5</v>
       </c>
-      <c r="M4" s="3">
+      <c r="M4" s="3" t="n">
         <v>128</v>
       </c>
-      <c r="N4" s="4">
+      <c r="N4" s="8" t="n">
         <v>0.034424</v>
       </c>
-      <c r="O4" s="5">
+      <c r="O4" s="5" t="n">
         <v>110</v>
       </c>
-      <c r="P4" s="5">
+      <c r="P4" s="5" t="n">
         <v>60</v>
       </c>
-      <c r="Q4" s="5">
+      <c r="Q4" s="5" t="n">
         <v>6</v>
       </c>
       <c r="R4" s="5" t="n">
         <v>50</v>
+      </c>
+      <c r="S4" s="3" t="n">
+        <v>262144</v>
+      </c>
+      <c r="T4" s="3" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/Config/Luban/source/TbGlobal.xlsx
+++ b/Config/Luban/source/TbGlobal.xlsx
@@ -1201,7 +1201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="14" outlineLevelRow="3"/>
   <cols>
     <col width="22" customWidth="1" style="6" min="1" max="13"/>
@@ -1209,6 +1209,9 @@
     <col width="40" customWidth="1" style="6" min="16" max="16"/>
     <col width="64" customWidth="1" style="6" min="19" max="19"/>
     <col width="64" customWidth="1" style="6" min="20" max="20"/>
+    <col width="30" customWidth="1" style="6" min="21" max="21"/>
+    <col width="30" customWidth="1" style="6" min="22" max="22"/>
+    <col width="30" customWidth="1" style="6" min="23" max="23"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.5" customHeight="1" s="6">
@@ -1312,6 +1315,21 @@
           <t>snapshotMaxInFlightRecords</t>
         </is>
       </c>
+      <c r="U1" s="7" t="inlineStr">
+        <is>
+          <t>foamCommitRate</t>
+        </is>
+      </c>
+      <c r="V1" s="7" t="inlineStr">
+        <is>
+          <t>foamDissolveRatio</t>
+        </is>
+      </c>
+      <c r="W1" s="7" t="inlineStr">
+        <is>
+          <t>foamSlopeDegrees</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="14.5" customHeight="1" s="6">
       <c r="A2" s="1" t="inlineStr">
@@ -1414,6 +1432,21 @@
           <t>int</t>
         </is>
       </c>
+      <c r="U2" s="1" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="V2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="W2" s="1" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="42" customHeight="1" s="6">
       <c r="A3" s="2" t="inlineStr">
@@ -1514,6 +1547,21 @@
       <c r="T3" s="2" t="inlineStr">
         <is>
           <t>每客户端未确认补同步记录上限（条，1到32）</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>泡沫：权威地形提交频率（Hz，整除模拟频率）</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>泡沫：敌方消融效率倍率</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>泡沫：自由坡面目标角度（度）</t>
         </is>
       </c>
     </row>
@@ -1576,6 +1624,15 @@
       <c r="T4" s="3" t="n">
         <v>8</v>
       </c>
+      <c r="U4" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="V4" s="3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W4" s="3" t="n">
+        <v>35</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Luban/source/TbGlobal.xlsx
+++ b/Config/Luban/source/TbGlobal.xlsx
@@ -1553,7 +1553,7 @@
         <v>0.5</v>
       </c>
       <c r="M4" s="3" t="n">
-        <v>128</v>
+        <v>256</v>
       </c>
       <c r="N4" s="8" t="n">
         <v>0.034424</v>
@@ -1571,7 +1571,7 @@
         <v>50</v>
       </c>
       <c r="S4" s="3" t="n">
-        <v>262144</v>
+        <v>1048576</v>
       </c>
       <c r="T4" s="3" t="n">
         <v>8</v>

--- a/Config/Luban/source/TbGlobal.xlsx
+++ b/Config/Luban/source/TbGlobal.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Re3b3415a95c14209"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Global" sheetId="1" r:id="Rd1f7e6b4c6e84dc4"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1118,6 +1118,10 @@
     <x:col min="26" max="26" width="36" hidden="0" customWidth="1"/>
     <x:col min="27" max="27" width="36" hidden="0" customWidth="1"/>
     <x:col min="28" max="28" width="36" hidden="0" customWidth="1"/>
+    <x:col min="29" max="29" width="40" hidden="0" customWidth="1"/>
+    <x:col min="30" max="30" width="40" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="40" hidden="0" customWidth="1"/>
+    <x:col min="32" max="32" width="40" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" s="6" customFormat="1" ht="14.5" customHeight="1">
@@ -1245,6 +1249,18 @@
       <x:c r="AB1" s="7" t="str">
         <x:v>blockNetworkBytesPerSecond</x:v>
       </x:c>
+      <x:c r="AC1" s="7" t="str">
+        <x:v>blockWorldTopHeight</x:v>
+      </x:c>
+      <x:c r="AD1" s="7" t="str">
+        <x:v>blockSpreadInterval</x:v>
+      </x:c>
+      <x:c r="AE1" s="7" t="str">
+        <x:v>blockSpreadMaxStepCells</x:v>
+      </x:c>
+      <x:c r="AF1" s="7" t="str">
+        <x:v>blockSpreadMinStackCells</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" s="6" customFormat="1" ht="14.5" customHeight="1">
       <x:c r="A2" s="1" t="inlineStr">
@@ -1371,6 +1387,18 @@
       <x:c r="AB2" s="1" t="str">
         <x:v>int</x:v>
       </x:c>
+      <x:c r="AC2" s="1" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AD2" s="1" t="str">
+        <x:v>float</x:v>
+      </x:c>
+      <x:c r="AE2" s="1" t="str">
+        <x:v>int</x:v>
+      </x:c>
+      <x:c r="AF2" s="1" t="str">
+        <x:v>int</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" s="6" customFormat="1" ht="42" customHeight="1">
       <x:c r="A3" s="2" t="inlineStr">
@@ -1496,6 +1524,18 @@
       </x:c>
       <x:c r="AB3" s="2" t="str">
         <x:v>积木：全房间传输预算（字节/秒）</x:v>
+      </x:c>
+      <x:c r="AC3" s="2" t="str">
+        <x:v>积木：全局建造顶界（世界Y，米）</x:v>
+      </x:c>
+      <x:c r="AD3" s="2" t="str">
+        <x:v>积木：守恒摊开间隔（秒）</x:v>
+      </x:c>
+      <x:c r="AE3" s="2" t="str">
+        <x:v>积木：摊开稳定邻列高差（格）</x:v>
+      </x:c>
+      <x:c r="AF3" s="2" t="str">
+        <x:v>积木：参与摊开的最少连续层数</x:v>
       </x:c>
     </x:row>
     <x:row r="4" s="6" customFormat="1" ht="14.5" customHeight="1">
@@ -1581,6 +1621,18 @@
       <x:c r="AB4" s="3" t="n">
         <x:v>2097152</x:v>
       </x:c>
+      <x:c r="AC4" s="3" t="n">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="AD4" s="3" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="AE4" s="3" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AF4" s="3" t="n">
+        <x:v>2</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
